--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-practitionerrole.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
